--- a/data/numeric/input/old_data_51/11.xlsx
+++ b/data/numeric/input/old_data_51/11.xlsx
@@ -2772,13 +2772,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C851DA75-452B-4F55-AE2D-F6FF753CA8B7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF238468-0F9E-48B2-8B52-E871CF0E76A2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1C678FA-DC21-4550-B867-52C6D3B41704}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D46D901C-DB31-4FB3-9DEF-0FA4C382ED79}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F41CCA8-4B3B-41CA-AF51-C7965FAC9E38}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{321B61B3-868B-4CE6-8E2E-4BAFDCA3C1D9}"/>
 </file>